--- a/data/data_xitu_LOOP3s.xlsx
+++ b/data/data_xitu_LOOP3s.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\jupyter\xitu\463\1117333\2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xitu\code_github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8B018E-18AD-4901-A52D-754A7D3A9E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A04B15-3EB7-4CE7-B3DC-ADA44C422854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -134,7 +139,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +161,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -165,7 +177,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -173,30 +185,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -502,7 +500,9 @@
   <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="29.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.15">
@@ -547,909 +547,910 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>1.224041888412714</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>0.63374549401921099</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>-1.464332317086781</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>0.33256741389405597</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>0.13495012889711391</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>1.0057097882892561</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="2">
         <v>0.62364511606867457</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>93</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>1.224041888412714</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>0.71315647866283449</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>-0.5512707306202751</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>0.44800016251129049</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>0.13495012889711391</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>-0.89720061778798854</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>0.49777821280380657</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>248</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>-1.768034739101952</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>1.5970184882897269</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>-1.0735166344612921</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>-0.86157785973402479</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>-2.1864047637458359</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>-0.80020250189020203</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>-0.40362484050750869</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>-0.75576800413263456</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>259</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>-1.768034739101952</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>1.5970184882897269</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>-0.47675719859744958</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>-0.86157785973402479</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>-2.1864047637458359</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>-0.80020250189020203</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>-0.40362484050750869</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>-0.84733079781228937</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>292</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>0.40460381705819531</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>0.20407120809139359</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>-0.47675719859744958</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>-0.5246305763414606</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>-6.7592357654909429E-3</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0.65878670240053772</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>1.7060027414464609</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>0.19130280186559309</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>342</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>-1.768034739101952</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>0.46888771386730638</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>-1.324817690899329</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>-2.0670705261686062</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>-0.92392717192502893</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>1.4690867525157401</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>0.22021409324456351</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>-1.6711762977602469</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>171</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>2.515004945655213E-2</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>-0.65754079283848765</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>0.67533048630194725</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>1.7201974624661061</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>1.3716159763129301</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>1.281476361593163</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>0.22021409324456351</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>1.1481050821155181</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>237</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>-1.768034739101952</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>1.5970184882897269</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>0.67533048630194725</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>-0.86157785973402479</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>-2.1864047637458359</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>-0.80020250189020203</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>-0.40362484050750869</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>-0.85374287538979332</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>314</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>0.40460381705819531</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>-2.3282425961109259</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>-1.0735166344612921</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>-0.69154276451931407</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>0.27638160230479508</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>-1.2964560205012861</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>1.5663035423197511</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="2">
         <v>-2.395178800126101</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>391</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>-5.3980791681490059E-2</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>1.3101898999712189</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>-0.47675719859744958</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>-1.507911908077513</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>-0.92392717192502893</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>-1.0417943004122521</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>0.22021409324456351</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="2">
         <v>-0.69784521430724922</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>134</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>-1.768034739101952</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>0.80219095013112429</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>0.28042872257099499</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>0.35482148209079911</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>-1.162048300626829</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>-0.61983758426583235</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="2">
         <v>0.50523547808337288</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>135</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>-1.768034739101952</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>0.80219095013112429</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>8.3854334736641736E-2</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>0.35482148209079911</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>-1.162048300626829</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>-0.61983758426583235</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>0.52150117698464549</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A14">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>1.224041888412714</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>0.63374549401921099</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>-1.427773571110875</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>0.33256741389405597</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>0.13495012889711391</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>1.0057097882892561</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>0.60088699185409944</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>67</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>1.224041888412714</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>0.71315647866283449</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>0.39519700083403159</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>0.44800016251129049</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>0.13495012889711391</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>-0.89720061778798854</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="2">
         <v>0.42991379893353199</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>89</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>1.224041888412714</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>0.71315647866283449</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>-0.73789675028082313</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>0.44800016251129049</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>0.13495012889711391</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>-0.89720061778798854</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="2">
         <v>0.43791557389193769</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>94</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>1.224041888412714</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>0.71315647866283449</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>-0.47675719859744958</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>0.44800016251129049</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>0.13495012889711391</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>-0.89720061778798854</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="2">
         <v>0.50677562419766131</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>128</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>0.29935489046220187</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>-0.22345000266932391</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>0.86242206665448629</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>0.45488281008522458</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>0.17712406545413881</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="2">
         <v>0.38731829122268541</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="2">
         <v>5.2235704011231378E-2</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="2">
         <v>0.49860714849705889</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>457</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>-5.3980791681490059E-2</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>-0.60785414180856134</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>-0.47675719859744958</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>1.395037931369991</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>1.209494945008277</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="2">
         <v>-0.7722381327925224</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="2">
         <v>-0.79331208017675403</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>0.87078272688850744</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>61</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>0.81808174297102587</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>-1.107090521830099</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>-0.47675719859744958</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>0.43889121330191178</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>-0.22973685625873999</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="2">
         <v>0.96509654207775752</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="2">
         <v>-0.12648877746261711</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>0.47668437037521588</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>146</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>-1.768034739101952</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>0.80219095013112429</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="2">
         <v>-1.6041157575828751</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>0.35482148209079911</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>-1.162048300626829</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="2">
         <v>-0.61983758426583235</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="2">
         <v>-1.091940327702678</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>0.64624077518115774</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>129</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>0.29935489046220187</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>-0.22345000266932391</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>6.3525267989051101E-2</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>0.45488281008522458</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>0.17712406545413881</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="2">
         <v>0.38731829122268541</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="2">
         <v>5.2235704011231378E-2</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="2">
         <v>0.51091660490674595</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>123</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>0.29935489046220187</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>-0.22345000266932391</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <v>-0.84488337732766283</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>0.45488281008522458</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>0.17712406545413881</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="2">
         <v>0.38731829122268541</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>5.2235704011231378E-2</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="2">
         <v>0.44018848003881422</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>